--- a/data/dividends_info_20260715.xlsx
+++ b/data/dividends_info_20260715.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>61.40999984741211</v>
+        <v>58.88000106811523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1465559358795418</v>
+        <v>0.152853258096724</v>
       </c>
       <c r="J2" t="n">
         <v>243</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.55000305175781</v>
+        <v>64.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.084430622627117</v>
+        <v>1.085271317829457</v>
       </c>
       <c r="J3" t="n">
         <v>222</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>9.279999732971191</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.646551742742235</v>
       </c>
       <c r="J4" t="n">
         <v>152</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>61.38999938964844</v>
+        <v>58.88000106811523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1466036828388954</v>
+        <v>0.152853258096724</v>
       </c>
       <c r="J6" t="n">
         <v>152</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.125</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I7" t="n">
-        <v>3.623529411764706</v>
+        <v>3.598130664738818</v>
       </c>
       <c r="J7" t="n">
         <v>131</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.61000061035156</v>
+        <v>21.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1.249421528802111</v>
+        <v>1.270588235294118</v>
       </c>
       <c r="J8" t="n">
         <v>131</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8510638067620513</v>
       </c>
       <c r="J10" t="n">
         <v>96</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.849999904632568</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7835051700455413</v>
+        <v>0.7786885063291337</v>
       </c>
       <c r="J13" t="n">
         <v>75</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.61000061035156</v>
+        <v>21.25</v>
       </c>
       <c r="I14" t="n">
-        <v>1.249421528802111</v>
+        <v>1.270588235294118</v>
       </c>
       <c r="J14" t="n">
         <v>68</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>61.38999938964844</v>
+        <v>58.88000106811523</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1466036828388954</v>
+        <v>0.152853258096724</v>
       </c>
       <c r="J15" t="n">
         <v>68</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.800000190734863</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="I16" t="n">
-        <v>5.172413623006964</v>
+        <v>5.190311230281897</v>
       </c>
       <c r="J16" t="n">
         <v>61</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.849999904632568</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7835051700455413</v>
+        <v>0.7786885063291337</v>
       </c>
       <c r="J18" t="n">
         <v>19</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.779999971389771</v>
+        <v>2.799999952316284</v>
       </c>
       <c r="I19" t="n">
-        <v>5.322625954058111</v>
+        <v>5.284607232853467</v>
       </c>
       <c r="J19" t="n">
         <v>19</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.78000020980835</v>
+        <v>5.789999961853027</v>
       </c>
       <c r="I20" t="n">
-        <v>4.325259358568248</v>
+        <v>4.317789320329981</v>
       </c>
       <c r="J20" t="n">
         <v>12</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.289999961853027</v>
+        <v>4.210000038146973</v>
       </c>
       <c r="I21" t="n">
-        <v>3.263403292421668</v>
+        <v>3.325415646827901</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>10.22000026702881</v>
+        <v>10.16399955749512</v>
       </c>
       <c r="I22" t="n">
-        <v>2.544031244683989</v>
+        <v>2.558048123961903</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>14.0600004196167</v>
+        <v>14.15999984741211</v>
       </c>
       <c r="I23" t="n">
-        <v>4.267425192696808</v>
+        <v>4.237288181254157</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.815999984741211</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="I24" t="n">
-        <v>7.812500042332844</v>
+        <v>7.829181654088743</v>
       </c>
       <c r="J24" t="n">
         <v>5</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5.699999809265137</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="I29" t="n">
-        <v>2.105263228341595</v>
+        <v>2.101576168096538</v>
       </c>
       <c r="J29" t="n">
         <v>-2</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5405405405405406</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="J30" t="n">
         <v>-2</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3.099999904632568</v>
+        <v>3.079999923706055</v>
       </c>
       <c r="I31" t="n">
-        <v>4.838709826275912</v>
+        <v>4.870129990766698</v>
       </c>
       <c r="J31" t="n">
         <v>-2</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.510000228881836</v>
+        <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>1.552106351386042</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="J33" t="n">
         <v>-9</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>36</v>
+        <v>35.59999847412109</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4213483326664756</v>
       </c>
       <c r="J34" t="n">
         <v>-9</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>21.5</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="I37" t="n">
-        <v>1.162790697674419</v>
+        <v>1.179245240580532</v>
       </c>
       <c r="J37" t="n">
         <v>-23</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>28.10000038146973</v>
+        <v>27.70000076293945</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6939501685152676</v>
+        <v>0.7039710997441398</v>
       </c>
       <c r="J38" t="n">
         <v>-23</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.889999985694885</v>
+        <v>1.924999952316284</v>
       </c>
       <c r="I39" t="n">
-        <v>1.746031759247188</v>
+        <v>1.714285756749878</v>
       </c>
       <c r="J39" t="n">
         <v>-23</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.059999942779541</v>
+        <v>5.09499979019165</v>
       </c>
       <c r="I40" t="n">
-        <v>5.731225361253625</v>
+        <v>5.691854993954602</v>
       </c>
       <c r="J40" t="n">
         <v>-23</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3.858000040054321</v>
+        <v>3.881999969482422</v>
       </c>
       <c r="I41" t="n">
-        <v>4.147226499192757</v>
+        <v>4.121586843323248</v>
       </c>
       <c r="J41" t="n">
         <v>-23</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.559999942779541</v>
+        <v>2.532000064849854</v>
       </c>
       <c r="I42" t="n">
-        <v>5.41406262101373</v>
+        <v>5.473933509090132</v>
       </c>
       <c r="J42" t="n">
         <v>-23</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>50.4900016784668</v>
+        <v>50.36999893188477</v>
       </c>
       <c r="I43" t="n">
-        <v>1.247771794526767</v>
+        <v>1.250744517290833</v>
       </c>
       <c r="J43" t="n">
         <v>-23</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>16.04999923706055</v>
+        <v>15.85000038146973</v>
       </c>
       <c r="I45" t="n">
-        <v>4.859813315124194</v>
+        <v>4.921135528248314</v>
       </c>
       <c r="J45" t="n">
         <v>-23</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>28.38999938964844</v>
+        <v>28.23999977111816</v>
       </c>
       <c r="I46" t="n">
-        <v>2.994012040415637</v>
+        <v>3.009915038559309</v>
       </c>
       <c r="J46" t="n">
         <v>-23</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>61.38999938964844</v>
+        <v>58.88000106811523</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1466036828388954</v>
+        <v>0.152853258096724</v>
       </c>
       <c r="J47" t="n">
         <v>-23</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>6.157999992370605</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="I49" t="n">
-        <v>2.944137710695353</v>
+        <v>2.952768793849701</v>
       </c>
       <c r="J49" t="n">
         <v>-23</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9.550000190734863</v>
+        <v>9.5</v>
       </c>
       <c r="I50" t="n">
-        <v>2.72251303463056</v>
+        <v>2.736842105263158</v>
       </c>
       <c r="J50" t="n">
         <v>-23</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>10.21000003814697</v>
+        <v>10.13500022888184</v>
       </c>
       <c r="I51" t="n">
-        <v>2.713026434525589</v>
+        <v>2.73310304631893</v>
       </c>
       <c r="J51" t="n">
         <v>-23</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.134999990463257</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="I52" t="n">
-        <v>1.189427322769395</v>
+        <v>1.194690270528077</v>
       </c>
       <c r="J52" t="n">
         <v>-30</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.970000028610229</v>
+        <v>3.007999897003174</v>
       </c>
       <c r="I53" t="n">
-        <v>3.703703668025653</v>
+        <v>3.656915018833325</v>
       </c>
       <c r="J53" t="n">
         <v>-30</v>
@@ -2990,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C217"/>
+  <dimension ref="A1:C227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3948,7 +3948,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3958,14 +3958,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3975,14 +3975,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3992,14 +3992,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4026,14 +4026,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4050,7 +4050,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4060,14 +4060,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4077,14 +4077,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4230,14 +4230,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4247,14 +4247,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4264,14 +4264,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4315,14 +4315,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4339,7 +4339,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4356,7 +4356,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4373,7 +4373,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4383,14 +4383,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4400,14 +4400,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -4434,14 +4434,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4458,7 +4458,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4485,14 +4485,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4519,14 +4519,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4536,14 +4536,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4553,14 +4553,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4570,14 +4570,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4587,14 +4587,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4628,7 +4628,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4645,7 +4645,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4662,7 +4662,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4689,14 +4689,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4713,7 +4713,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4740,14 +4740,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4757,14 +4757,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4791,14 +4791,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4815,7 +4815,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4842,14 +4842,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4876,14 +4876,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4910,14 +4910,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4934,7 +4934,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4944,14 +4944,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4985,7 +4985,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4995,14 +4995,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5012,14 +5012,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5053,7 +5053,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5070,7 +5070,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5087,7 +5087,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5131,14 +5131,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5189,7 +5189,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5240,7 +5240,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5250,14 +5250,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5267,14 +5267,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5284,14 +5284,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5342,7 +5342,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5359,7 +5359,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5386,36 +5386,36 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5427,29 +5427,29 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5461,46 +5461,46 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5512,24 +5512,24 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5546,7 +5546,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5556,14 +5556,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5580,7 +5580,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5597,7 +5597,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5607,14 +5607,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5624,14 +5624,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5641,53 +5641,53 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5699,63 +5699,63 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5767,12 +5767,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5784,46 +5784,46 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5835,12 +5835,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5852,29 +5852,29 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5886,12 +5886,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5903,29 +5903,29 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5937,7 +5937,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5947,14 +5947,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5971,7 +5971,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6005,29 +6005,29 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6039,12 +6039,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6056,114 +6056,114 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6175,7 +6175,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6192,7 +6192,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6226,7 +6226,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6243,7 +6243,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6270,14 +6270,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6294,7 +6294,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6304,14 +6304,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6328,29 +6328,29 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6362,114 +6362,114 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6481,12 +6481,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6498,7 +6498,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6542,14 +6542,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6576,14 +6576,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6593,14 +6593,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6617,46 +6617,46 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6668,15 +6668,185 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
+          <t>REVO Insurance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Bper Banca S.P.A.</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>F.I.L.A. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>BANCA SISTEMA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>GEFRAN S.p.A.</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Riba Mundo Tecnologia S.A.</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Half Year Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>EMAK S.p.A.</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
           <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>Half Year Preliminary Results</t>
         </is>
@@ -6693,104 +6863,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PIQUADRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0004240443</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-08-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2.779999971389771</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.147969</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>5.322625954058111</v>
-      </c>
-      <c r="I2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6801,61 +6876,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>